--- a/SyncLogs/SynchronizeLogAllEntries - tasks.xlsx
+++ b/SyncLogs/SynchronizeLogAllEntries - tasks.xlsx
@@ -20,366 +20,366 @@
     <t>cell_address</t>
   </si>
   <si>
+    <t>40,5</t>
+  </si>
+  <si>
+    <t>40,6</t>
+  </si>
+  <si>
+    <t>41,5</t>
+  </si>
+  <si>
+    <t>48,5</t>
+  </si>
+  <si>
+    <t>48,6</t>
+  </si>
+  <si>
+    <t>49,5</t>
+  </si>
+  <si>
+    <t>49,6</t>
+  </si>
+  <si>
+    <t>50,5</t>
+  </si>
+  <si>
+    <t>50,6</t>
+  </si>
+  <si>
+    <t>51,5</t>
+  </si>
+  <si>
+    <t>51,6</t>
+  </si>
+  <si>
+    <t>52,5</t>
+  </si>
+  <si>
+    <t>52,6</t>
+  </si>
+  <si>
+    <t>18,6</t>
+  </si>
+  <si>
+    <t>19,5</t>
+  </si>
+  <si>
+    <t>19,6</t>
+  </si>
+  <si>
+    <t>20,5</t>
+  </si>
+  <si>
+    <t>20,6</t>
+  </si>
+  <si>
+    <t>21,5</t>
+  </si>
+  <si>
+    <t>21,6</t>
+  </si>
+  <si>
+    <t>22,5</t>
+  </si>
+  <si>
+    <t>22,6</t>
+  </si>
+  <si>
+    <t>23,5</t>
+  </si>
+  <si>
+    <t>23,6</t>
+  </si>
+  <si>
+    <t>24,5</t>
+  </si>
+  <si>
+    <t>24,6</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>3,6</t>
+  </si>
+  <si>
+    <t>4,5</t>
+  </si>
+  <si>
+    <t>4,6</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>5,6</t>
+  </si>
+  <si>
+    <t>6,5</t>
+  </si>
+  <si>
+    <t>6,6</t>
+  </si>
+  <si>
+    <t>7,5</t>
+  </si>
+  <si>
+    <t>7,6</t>
+  </si>
+  <si>
+    <t>8,5</t>
+  </si>
+  <si>
+    <t>8,6</t>
+  </si>
+  <si>
+    <t>9,5</t>
+  </si>
+  <si>
+    <t>9,6</t>
+  </si>
+  <si>
+    <t>10,5</t>
+  </si>
+  <si>
+    <t>10,6</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>18,5</t>
+  </si>
+  <si>
+    <t>25,5</t>
+  </si>
+  <si>
+    <t>25,6</t>
+  </si>
+  <si>
+    <t>26,5</t>
+  </si>
+  <si>
+    <t>33,5</t>
+  </si>
+  <si>
+    <t>33,6</t>
+  </si>
+  <si>
+    <t>34,5</t>
+  </si>
+  <si>
+    <t>34,6</t>
+  </si>
+  <si>
+    <t>35,5</t>
+  </si>
+  <si>
+    <t>35,6</t>
+  </si>
+  <si>
+    <t>36,5</t>
+  </si>
+  <si>
+    <t>36,6</t>
+  </si>
+  <si>
+    <t>37,5</t>
+  </si>
+  <si>
+    <t>37,6</t>
+  </si>
+  <si>
+    <t>38,5</t>
+  </si>
+  <si>
+    <t>38,6</t>
+  </si>
+  <si>
+    <t>39,5</t>
+  </si>
+  <si>
+    <t>39,6</t>
+  </si>
+  <si>
+    <t>53,5</t>
+  </si>
+  <si>
+    <t>53,6</t>
+  </si>
+  <si>
+    <t>54,5</t>
+  </si>
+  <si>
+    <t>54,6</t>
+  </si>
+  <si>
+    <t>55,5</t>
+  </si>
+  <si>
+    <t>55,6</t>
+  </si>
+  <si>
     <t>56,5</t>
   </si>
   <si>
-    <t>55,6</t>
-  </si>
-  <si>
-    <t>55,5</t>
-  </si>
-  <si>
-    <t>39,6</t>
-  </si>
-  <si>
-    <t>39,5</t>
-  </si>
-  <si>
-    <t>38,6</t>
-  </si>
-  <si>
-    <t>38,5</t>
-  </si>
-  <si>
-    <t>37,6</t>
-  </si>
-  <si>
-    <t>37,5</t>
-  </si>
-  <si>
-    <t>36,6</t>
-  </si>
-  <si>
-    <t>36,5</t>
-  </si>
-  <si>
-    <t>35,6</t>
-  </si>
-  <si>
-    <t>35,5</t>
-  </si>
-  <si>
-    <t>34,6</t>
-  </si>
-  <si>
-    <t>34,5</t>
-  </si>
-  <si>
-    <t>33,6</t>
+    <t>56,6</t>
+  </si>
+  <si>
+    <t>57,5</t>
+  </si>
+  <si>
+    <t>57,6</t>
+  </si>
+  <si>
+    <t>58,5</t>
+  </si>
+  <si>
+    <t>58,6</t>
+  </si>
+  <si>
+    <t>59,5</t>
+  </si>
+  <si>
+    <t>59,6</t>
+  </si>
+  <si>
+    <t>60,5</t>
+  </si>
+  <si>
+    <t>60,6</t>
+  </si>
+  <si>
+    <t>61,5</t>
+  </si>
+  <si>
+    <t>61,6</t>
+  </si>
+  <si>
+    <t>62,5</t>
+  </si>
+  <si>
+    <t>62,6</t>
+  </si>
+  <si>
+    <t>41,6</t>
+  </si>
+  <si>
+    <t>42,5</t>
+  </si>
+  <si>
+    <t>42,6</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>43,6</t>
+  </si>
+  <si>
+    <t>44,5</t>
+  </si>
+  <si>
+    <t>44,6</t>
+  </si>
+  <si>
+    <t>45,5</t>
+  </si>
+  <si>
+    <t>45,6</t>
+  </si>
+  <si>
+    <t>46,5</t>
+  </si>
+  <si>
+    <t>46,6</t>
+  </si>
+  <si>
+    <t>47,5</t>
+  </si>
+  <si>
+    <t>47,6</t>
+  </si>
+  <si>
+    <t>26,6</t>
+  </si>
+  <si>
+    <t>27,5</t>
+  </si>
+  <si>
+    <t>27,6</t>
+  </si>
+  <si>
+    <t>28,5</t>
+  </si>
+  <si>
+    <t>28,6</t>
+  </si>
+  <si>
+    <t>29,5</t>
+  </si>
+  <si>
+    <t>29,6</t>
+  </si>
+  <si>
+    <t>30,5</t>
+  </si>
+  <si>
+    <t>30,6</t>
+  </si>
+  <si>
+    <t>31,5</t>
+  </si>
+  <si>
+    <t>31,6</t>
+  </si>
+  <si>
+    <t>32,5</t>
+  </si>
+  <si>
+    <t>32,6</t>
+  </si>
+  <si>
+    <t>11,6</t>
+  </si>
+  <si>
+    <t>12,5</t>
+  </si>
+  <si>
+    <t>12,6</t>
+  </si>
+  <si>
+    <t>13,5</t>
+  </si>
+  <si>
+    <t>13,6</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>14,6</t>
+  </si>
+  <si>
+    <t>15,5</t>
+  </si>
+  <si>
+    <t>15,6</t>
+  </si>
+  <si>
+    <t>16,5</t>
+  </si>
+  <si>
+    <t>16,6</t>
+  </si>
+  <si>
+    <t>17,5</t>
   </si>
   <si>
     <t>17,6</t>
   </si>
   <si>
-    <t>17,5</t>
-  </si>
-  <si>
-    <t>16,6</t>
-  </si>
-  <si>
-    <t>16,5</t>
-  </si>
-  <si>
-    <t>15,6</t>
-  </si>
-  <si>
-    <t>15,5</t>
-  </si>
-  <si>
-    <t>14,6</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>13,6</t>
-  </si>
-  <si>
-    <t>13,5</t>
-  </si>
-  <si>
-    <t>12,6</t>
-  </si>
-  <si>
-    <t>12,5</t>
-  </si>
-  <si>
-    <t>18,5</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>10,6</t>
-  </si>
-  <si>
-    <t>10,5</t>
-  </si>
-  <si>
-    <t>9,6</t>
-  </si>
-  <si>
-    <t>9,5</t>
-  </si>
-  <si>
-    <t>8,6</t>
-  </si>
-  <si>
-    <t>8,5</t>
-  </si>
-  <si>
-    <t>7,6</t>
-  </si>
-  <si>
-    <t>7,5</t>
-  </si>
-  <si>
-    <t>6,6</t>
-  </si>
-  <si>
-    <t>6,5</t>
-  </si>
-  <si>
-    <t>5,6</t>
-  </si>
-  <si>
-    <t>11,6</t>
-  </si>
-  <si>
-    <t>32,6</t>
-  </si>
-  <si>
-    <t>32,5</t>
-  </si>
-  <si>
-    <t>31,6</t>
-  </si>
-  <si>
-    <t>31,5</t>
-  </si>
-  <si>
-    <t>30,6</t>
-  </si>
-  <si>
-    <t>30,5</t>
-  </si>
-  <si>
-    <t>29,6</t>
-  </si>
-  <si>
-    <t>29,5</t>
-  </si>
-  <si>
-    <t>28,6</t>
-  </si>
-  <si>
-    <t>28,5</t>
-  </si>
-  <si>
-    <t>27,6</t>
-  </si>
-  <si>
-    <t>27,5</t>
-  </si>
-  <si>
-    <t>26,6</t>
-  </si>
-  <si>
-    <t>47,6</t>
-  </si>
-  <si>
-    <t>47,5</t>
-  </si>
-  <si>
-    <t>46,6</t>
-  </si>
-  <si>
-    <t>46,5</t>
-  </si>
-  <si>
-    <t>45,6</t>
-  </si>
-  <si>
-    <t>45,5</t>
-  </si>
-  <si>
-    <t>44,6</t>
-  </si>
-  <si>
-    <t>44,5</t>
-  </si>
-  <si>
-    <t>43,6</t>
-  </si>
-  <si>
-    <t>43,5</t>
-  </si>
-  <si>
-    <t>42,6</t>
-  </si>
-  <si>
-    <t>42,5</t>
-  </si>
-  <si>
-    <t>41,6</t>
-  </si>
-  <si>
-    <t>62,6</t>
-  </si>
-  <si>
-    <t>62,5</t>
-  </si>
-  <si>
-    <t>61,6</t>
-  </si>
-  <si>
-    <t>61,5</t>
-  </si>
-  <si>
-    <t>60,6</t>
-  </si>
-  <si>
-    <t>60,5</t>
-  </si>
-  <si>
-    <t>59,6</t>
-  </si>
-  <si>
-    <t>59,5</t>
-  </si>
-  <si>
-    <t>58,6</t>
-  </si>
-  <si>
-    <t>58,5</t>
-  </si>
-  <si>
-    <t>57,6</t>
-  </si>
-  <si>
-    <t>57,5</t>
-  </si>
-  <si>
-    <t>56,6</t>
-  </si>
-  <si>
-    <t>54,6</t>
-  </si>
-  <si>
-    <t>54,5</t>
-  </si>
-  <si>
-    <t>53,6</t>
-  </si>
-  <si>
-    <t>53,5</t>
-  </si>
-  <si>
-    <t>52,6</t>
-  </si>
-  <si>
-    <t>52,5</t>
-  </si>
-  <si>
-    <t>51,6</t>
-  </si>
-  <si>
-    <t>51,5</t>
-  </si>
-  <si>
-    <t>50,6</t>
-  </si>
-  <si>
-    <t>50,5</t>
-  </si>
-  <si>
-    <t>49,6</t>
-  </si>
-  <si>
-    <t>49,5</t>
-  </si>
-  <si>
-    <t>48,6</t>
-  </si>
-  <si>
-    <t>48,5</t>
-  </si>
-  <si>
-    <t>41,5</t>
-  </si>
-  <si>
-    <t>40,6</t>
-  </si>
-  <si>
-    <t>40,5</t>
-  </si>
-  <si>
-    <t>33,5</t>
-  </si>
-  <si>
-    <t>26,5</t>
-  </si>
-  <si>
-    <t>25,6</t>
-  </si>
-  <si>
-    <t>25,5</t>
-  </si>
-  <si>
-    <t>24,6</t>
-  </si>
-  <si>
-    <t>24,5</t>
-  </si>
-  <si>
-    <t>23,6</t>
-  </si>
-  <si>
-    <t>23,5</t>
-  </si>
-  <si>
-    <t>22,6</t>
-  </si>
-  <si>
-    <t>22,5</t>
-  </si>
-  <si>
-    <t>21,6</t>
-  </si>
-  <si>
-    <t>21,5</t>
-  </si>
-  <si>
-    <t>20,6</t>
-  </si>
-  <si>
-    <t>20,5</t>
-  </si>
-  <si>
-    <t>19,6</t>
-  </si>
-  <si>
-    <t>19,5</t>
-  </si>
-  <si>
-    <t>18,6</t>
-  </si>
-  <si>
-    <t>5,5</t>
-  </si>
-  <si>
-    <t>4,6</t>
-  </si>
-  <si>
-    <t>4,5</t>
-  </si>
-  <si>
-    <t>3,6</t>
-  </si>
-  <si>
-    <t>3,5</t>
-  </si>
-  <si>
     <t>cell_address2</t>
   </si>
   <si>
@@ -464,184 +464,184 @@
     <t>time_slice</t>
   </si>
   <si>
+    <t>S02WD2P</t>
+  </si>
+  <si>
+    <t>S02WD2Y</t>
+  </si>
+  <si>
+    <t>S03WD2F</t>
+  </si>
+  <si>
+    <t>S03WD2G</t>
+  </si>
+  <si>
+    <t>S03WD2P</t>
+  </si>
+  <si>
+    <t>S03WD2Y</t>
+  </si>
+  <si>
+    <t>S03WD2Z</t>
+  </si>
+  <si>
+    <t>S01WD2F</t>
+  </si>
+  <si>
+    <t>S01WD2G</t>
+  </si>
+  <si>
+    <t>S01WD2P</t>
+  </si>
+  <si>
+    <t>S01WD2Y</t>
+  </si>
+  <si>
+    <t>S01WD2Z</t>
+  </si>
+  <si>
+    <t>S02WD1A</t>
+  </si>
+  <si>
+    <t>S02WD1B</t>
+  </si>
+  <si>
+    <t>S01WD1A</t>
+  </si>
+  <si>
+    <t>S01WD1B</t>
+  </si>
+  <si>
+    <t>S01WD1C</t>
+  </si>
+  <si>
+    <t>S01WD1D</t>
+  </si>
+  <si>
+    <t>S01WD1E</t>
+  </si>
+  <si>
+    <t>S01WD1F</t>
+  </si>
+  <si>
+    <t>S01WD1G</t>
+  </si>
+  <si>
+    <t>S01WD1P</t>
+  </si>
+  <si>
+    <t>S01WD1Y</t>
+  </si>
+  <si>
+    <t>S02WD1C</t>
+  </si>
+  <si>
+    <t>S02WD1D</t>
+  </si>
+  <si>
+    <t>S02WD2A</t>
+  </si>
+  <si>
+    <t>S02WD2B</t>
+  </si>
+  <si>
+    <t>S02WD2C</t>
+  </si>
+  <si>
+    <t>S02WD2D</t>
+  </si>
+  <si>
+    <t>S02WD2E</t>
+  </si>
+  <si>
+    <t>S02WD2F</t>
+  </si>
+  <si>
+    <t>S02WD2G</t>
+  </si>
+  <si>
+    <t>S03WD1A</t>
+  </si>
+  <si>
+    <t>S03WD1B</t>
+  </si>
+  <si>
+    <t>S03WD1C</t>
+  </si>
+  <si>
     <t>S03WD1D</t>
   </si>
   <si>
-    <t>S03WD1C</t>
-  </si>
-  <si>
-    <t>S02WD2G</t>
-  </si>
-  <si>
-    <t>S02WD2F</t>
-  </si>
-  <si>
-    <t>S02WD2E</t>
-  </si>
-  <si>
-    <t>S02WD2D</t>
-  </si>
-  <si>
-    <t>S02WD2C</t>
-  </si>
-  <si>
-    <t>S02WD2B</t>
-  </si>
-  <si>
-    <t>S02WD2A</t>
+    <t>S03WD1E</t>
+  </si>
+  <si>
+    <t>S03WD1F</t>
+  </si>
+  <si>
+    <t>S03WD1G</t>
+  </si>
+  <si>
+    <t>S03WD1P</t>
+  </si>
+  <si>
+    <t>S03WD1Y</t>
+  </si>
+  <si>
+    <t>S03WD1Z</t>
+  </si>
+  <si>
+    <t>S02WD2Z</t>
+  </si>
+  <si>
+    <t>S03WD2A</t>
+  </si>
+  <si>
+    <t>S03WD2B</t>
+  </si>
+  <si>
+    <t>S03WD2C</t>
+  </si>
+  <si>
+    <t>S03WD2D</t>
+  </si>
+  <si>
+    <t>S03WD2E</t>
+  </si>
+  <si>
+    <t>S02WD1E</t>
+  </si>
+  <si>
+    <t>S02WD1F</t>
+  </si>
+  <si>
+    <t>S02WD1G</t>
+  </si>
+  <si>
+    <t>S02WD1P</t>
+  </si>
+  <si>
+    <t>S02WD1Y</t>
+  </si>
+  <si>
+    <t>S02WD1Z</t>
+  </si>
+  <si>
+    <t>S01WD1Z</t>
+  </si>
+  <si>
+    <t>S01WD2A</t>
+  </si>
+  <si>
+    <t>S01WD2B</t>
+  </si>
+  <si>
+    <t>S01WD2C</t>
+  </si>
+  <si>
+    <t>S01WD2D</t>
   </si>
   <si>
     <t>S01WD2E</t>
-  </si>
-  <si>
-    <t>S01WD2D</t>
-  </si>
-  <si>
-    <t>S01WD2C</t>
-  </si>
-  <si>
-    <t>S01WD2B</t>
-  </si>
-  <si>
-    <t>S01WD2A</t>
-  </si>
-  <si>
-    <t>S01WD1Z</t>
-  </si>
-  <si>
-    <t>S01WD2F</t>
-  </si>
-  <si>
-    <t>S01WD1Y</t>
-  </si>
-  <si>
-    <t>S01WD1P</t>
-  </si>
-  <si>
-    <t>S01WD1G</t>
-  </si>
-  <si>
-    <t>S01WD1F</t>
-  </si>
-  <si>
-    <t>S01WD1E</t>
-  </si>
-  <si>
-    <t>S01WD1D</t>
-  </si>
-  <si>
-    <t>S01WD1C</t>
-  </si>
-  <si>
-    <t>S02WD1Z</t>
-  </si>
-  <si>
-    <t>S02WD1Y</t>
-  </si>
-  <si>
-    <t>S02WD1P</t>
-  </si>
-  <si>
-    <t>S02WD1G</t>
-  </si>
-  <si>
-    <t>S02WD1F</t>
-  </si>
-  <si>
-    <t>S02WD1E</t>
-  </si>
-  <si>
-    <t>S02WD1D</t>
-  </si>
-  <si>
-    <t>S03WD2E</t>
-  </si>
-  <si>
-    <t>S03WD2D</t>
-  </si>
-  <si>
-    <t>S03WD2C</t>
-  </si>
-  <si>
-    <t>S03WD2B</t>
-  </si>
-  <si>
-    <t>S03WD2A</t>
-  </si>
-  <si>
-    <t>S02WD2Z</t>
-  </si>
-  <si>
-    <t>S02WD2Y</t>
-  </si>
-  <si>
-    <t>S03WD1Z</t>
-  </si>
-  <si>
-    <t>S03WD1Y</t>
-  </si>
-  <si>
-    <t>S03WD1P</t>
-  </si>
-  <si>
-    <t>S03WD1G</t>
-  </si>
-  <si>
-    <t>S03WD1F</t>
-  </si>
-  <si>
-    <t>S03WD1E</t>
-  </si>
-  <si>
-    <t>S03WD1B</t>
-  </si>
-  <si>
-    <t>S03WD1A</t>
-  </si>
-  <si>
-    <t>S03WD2Z</t>
-  </si>
-  <si>
-    <t>S03WD2Y</t>
-  </si>
-  <si>
-    <t>S03WD2P</t>
-  </si>
-  <si>
-    <t>S03WD2G</t>
-  </si>
-  <si>
-    <t>S03WD2F</t>
-  </si>
-  <si>
-    <t>S02WD2P</t>
-  </si>
-  <si>
-    <t>S02WD1C</t>
-  </si>
-  <si>
-    <t>S02WD1B</t>
-  </si>
-  <si>
-    <t>S02WD1A</t>
-  </si>
-  <si>
-    <t>S01WD2Z</t>
-  </si>
-  <si>
-    <t>S01WD2Y</t>
-  </si>
-  <si>
-    <t>S01WD2P</t>
-  </si>
-  <si>
-    <t>S01WD2G</t>
-  </si>
-  <si>
-    <t>S01WD1B</t>
-  </si>
-  <si>
-    <t>S01WD1A</t>
   </si>
   <si>
     <t>time_slice2</t>
@@ -1224,7 +1224,7 @@
         <v>124</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.005512073</v>
+        <v>0.006738811</v>
       </c>
       <c r="AC2" t="s">
         <v>217</v>
@@ -1304,7 +1304,7 @@
         <v>124</v>
       </c>
       <c r="W3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="X3" t="s">
         <v>124</v>
@@ -1319,7 +1319,7 @@
         <v>124</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.005703369</v>
+        <v>0.006931423</v>
       </c>
       <c r="AC3" t="s">
         <v>217</v>
@@ -1414,7 +1414,7 @@
         <v>124</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.005548685</v>
+        <v>0.006423248</v>
       </c>
       <c r="AC4" t="s">
         <v>217</v>
@@ -1461,7 +1461,7 @@
         <v>134</v>
       </c>
       <c r="L5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M5" t="s">
         <v>124</v>
@@ -1509,7 +1509,7 @@
         <v>124</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.006923147</v>
+        <v>0.002444422</v>
       </c>
       <c r="AC5" t="s">
         <v>217</v>
@@ -1556,7 +1556,7 @@
         <v>134</v>
       </c>
       <c r="L6" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M6" t="s">
         <v>124</v>
@@ -1604,7 +1604,7 @@
         <v>124</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.006971473</v>
+        <v>0.001969919</v>
       </c>
       <c r="AC6" t="s">
         <v>217</v>
@@ -1651,7 +1651,7 @@
         <v>134</v>
       </c>
       <c r="L7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M7" t="s">
         <v>124</v>
@@ -1699,7 +1699,7 @@
         <v>124</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.006495451</v>
+        <v>0.002498876</v>
       </c>
       <c r="AC7" t="s">
         <v>217</v>
@@ -1746,7 +1746,7 @@
         <v>134</v>
       </c>
       <c r="L8" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M8" t="s">
         <v>124</v>
@@ -1794,7 +1794,7 @@
         <v>124</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.006878595</v>
+        <v>0.002380284</v>
       </c>
       <c r="AC8" t="s">
         <v>217</v>
@@ -1841,7 +1841,7 @@
         <v>134</v>
       </c>
       <c r="L9" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M9" t="s">
         <v>124</v>
@@ -1889,7 +1889,7 @@
         <v>124</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.042025038</v>
+        <v>0.002438007</v>
       </c>
       <c r="AC9" t="s">
         <v>217</v>
@@ -1936,7 +1936,7 @@
         <v>134</v>
       </c>
       <c r="L10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M10" t="s">
         <v>124</v>
@@ -1984,7 +1984,7 @@
         <v>124</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.045655947</v>
+        <v>0.002537856</v>
       </c>
       <c r="AC10" t="s">
         <v>217</v>
@@ -2031,7 +2031,7 @@
         <v>134</v>
       </c>
       <c r="L11" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M11" t="s">
         <v>124</v>
@@ -2079,7 +2079,7 @@
         <v>124</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.005426907</v>
+        <v>0.002326722</v>
       </c>
       <c r="AC11" t="s">
         <v>217</v>
@@ -2126,7 +2126,7 @@
         <v>134</v>
       </c>
       <c r="L12" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M12" t="s">
         <v>124</v>
@@ -2174,7 +2174,7 @@
         <v>124</v>
       </c>
       <c r="AB12" t="n">
-        <v>0.005789925</v>
+        <v>0.002350475</v>
       </c>
       <c r="AC12" t="s">
         <v>217</v>
@@ -2221,7 +2221,7 @@
         <v>134</v>
       </c>
       <c r="L13" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M13" t="s">
         <v>124</v>
@@ -2269,7 +2269,7 @@
         <v>124</v>
       </c>
       <c r="AB13" t="n">
-        <v>0.004944183</v>
+        <v>0.008188906</v>
       </c>
       <c r="AC13" t="s">
         <v>217</v>
@@ -2316,7 +2316,7 @@
         <v>134</v>
       </c>
       <c r="L14" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M14" t="s">
         <v>124</v>
@@ -2364,7 +2364,7 @@
         <v>124</v>
       </c>
       <c r="AB14" t="n">
-        <v>0.005624833</v>
+        <v>0.007518359</v>
       </c>
       <c r="AC14" t="s">
         <v>217</v>
@@ -2459,7 +2459,7 @@
         <v>124</v>
       </c>
       <c r="AB15" t="n">
-        <v>0.004400825</v>
+        <v>0.004516368</v>
       </c>
       <c r="AC15" t="s">
         <v>217</v>
@@ -2539,7 +2539,7 @@
         <v>124</v>
       </c>
       <c r="W16" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="X16" t="s">
         <v>124</v>
@@ -2554,7 +2554,7 @@
         <v>124</v>
       </c>
       <c r="AB16" t="n">
-        <v>0.005459863</v>
+        <v>0.004193503</v>
       </c>
       <c r="AC16" t="s">
         <v>217</v>
@@ -2649,7 +2649,7 @@
         <v>124</v>
       </c>
       <c r="AB17" t="n">
-        <v>0.024544266</v>
+        <v>0.004690154</v>
       </c>
       <c r="AC17" t="s">
         <v>217</v>
@@ -2696,7 +2696,7 @@
         <v>134</v>
       </c>
       <c r="L18" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s">
         <v>124</v>
@@ -2744,7 +2744,7 @@
         <v>124</v>
       </c>
       <c r="AB18" t="n">
-        <v>0.030742214</v>
+        <v>0.00416601</v>
       </c>
       <c r="AC18" t="s">
         <v>217</v>
@@ -2791,7 +2791,7 @@
         <v>134</v>
       </c>
       <c r="L19" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s">
         <v>124</v>
@@ -2839,7 +2839,7 @@
         <v>124</v>
       </c>
       <c r="AB19" t="n">
-        <v>0.029224619</v>
+        <v>0.004582276</v>
       </c>
       <c r="AC19" t="s">
         <v>217</v>
@@ -2886,7 +2886,7 @@
         <v>134</v>
       </c>
       <c r="L20" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M20" t="s">
         <v>124</v>
@@ -2934,7 +2934,7 @@
         <v>124</v>
       </c>
       <c r="AB20" t="n">
-        <v>0.003610349</v>
+        <v>0.004127151</v>
       </c>
       <c r="AC20" t="s">
         <v>217</v>
@@ -2981,7 +2981,7 @@
         <v>134</v>
       </c>
       <c r="L21" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M21" t="s">
         <v>124</v>
@@ -3029,7 +3029,7 @@
         <v>124</v>
       </c>
       <c r="AB21" t="n">
-        <v>0.00392837</v>
+        <v>0.004342057</v>
       </c>
       <c r="AC21" t="s">
         <v>217</v>
@@ -3076,7 +3076,7 @@
         <v>134</v>
       </c>
       <c r="L22" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M22" t="s">
         <v>124</v>
@@ -3124,7 +3124,7 @@
         <v>124</v>
       </c>
       <c r="AB22" t="n">
-        <v>0.003281807</v>
+        <v>0.016337457</v>
       </c>
       <c r="AC22" t="s">
         <v>217</v>
@@ -3171,7 +3171,7 @@
         <v>134</v>
       </c>
       <c r="L23" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M23" t="s">
         <v>124</v>
@@ -3219,7 +3219,7 @@
         <v>124</v>
       </c>
       <c r="AB23" t="n">
-        <v>0.003855268</v>
+        <v>0.013371994</v>
       </c>
       <c r="AC23" t="s">
         <v>217</v>
@@ -3266,7 +3266,7 @@
         <v>134</v>
       </c>
       <c r="L24" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M24" t="s">
         <v>124</v>
@@ -3314,7 +3314,7 @@
         <v>124</v>
       </c>
       <c r="AB24" t="n">
-        <v>0.002924553</v>
+        <v>0.080785628</v>
       </c>
       <c r="AC24" t="s">
         <v>217</v>
@@ -3361,7 +3361,7 @@
         <v>134</v>
       </c>
       <c r="L25" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M25" t="s">
         <v>124</v>
@@ -3409,7 +3409,7 @@
         <v>124</v>
       </c>
       <c r="AB25" t="n">
-        <v>0.003792878</v>
+        <v>0.065697347</v>
       </c>
       <c r="AC25" t="s">
         <v>217</v>
@@ -3456,7 +3456,7 @@
         <v>134</v>
       </c>
       <c r="L26" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M26" t="s">
         <v>124</v>
@@ -3504,7 +3504,7 @@
         <v>124</v>
       </c>
       <c r="AB26" t="n">
-        <v>0.015902671</v>
+        <v>0.014058032</v>
       </c>
       <c r="AC26" t="s">
         <v>217</v>
@@ -3551,7 +3551,7 @@
         <v>134</v>
       </c>
       <c r="L27" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M27" t="s">
         <v>124</v>
@@ -3599,7 +3599,7 @@
         <v>124</v>
       </c>
       <c r="AB27" t="n">
-        <v>0.02187069</v>
+        <v>0.01394809</v>
       </c>
       <c r="AC27" t="s">
         <v>217</v>
@@ -3646,7 +3646,7 @@
         <v>134</v>
       </c>
       <c r="L28" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M28" t="s">
         <v>124</v>
@@ -3694,7 +3694,7 @@
         <v>124</v>
       </c>
       <c r="AB28" t="n">
-        <v>0.037675262</v>
+        <v>0.053937877</v>
       </c>
       <c r="AC28" t="s">
         <v>217</v>
@@ -3741,7 +3741,7 @@
         <v>134</v>
       </c>
       <c r="L29" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M29" t="s">
         <v>124</v>
@@ -3789,7 +3789,7 @@
         <v>124</v>
       </c>
       <c r="AB29" t="n">
-        <v>0.036646967</v>
+        <v>0.045285979</v>
       </c>
       <c r="AC29" t="s">
         <v>217</v>
@@ -3884,7 +3884,7 @@
         <v>124</v>
       </c>
       <c r="AB30" t="n">
-        <v>0.004239412</v>
+        <v>0.009470893</v>
       </c>
       <c r="AC30" t="s">
         <v>217</v>
@@ -3931,7 +3931,7 @@
         <v>134</v>
       </c>
       <c r="L31" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M31" t="s">
         <v>124</v>
@@ -3964,7 +3964,7 @@
         <v>124</v>
       </c>
       <c r="W31" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="X31" t="s">
         <v>124</v>
@@ -3979,7 +3979,7 @@
         <v>124</v>
       </c>
       <c r="AB31" t="n">
-        <v>0.009416124</v>
+        <v>0.010118339</v>
       </c>
       <c r="AC31" t="s">
         <v>217</v>
@@ -4026,7 +4026,7 @@
         <v>134</v>
       </c>
       <c r="L32" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M32" t="s">
         <v>124</v>
@@ -4059,7 +4059,7 @@
         <v>124</v>
       </c>
       <c r="W32" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="X32" t="s">
         <v>124</v>
@@ -4074,7 +4074,7 @@
         <v>124</v>
       </c>
       <c r="AB32" t="n">
-        <v>0.011095322</v>
+        <v>0.009772012</v>
       </c>
       <c r="AC32" t="s">
         <v>217</v>
@@ -4121,7 +4121,7 @@
         <v>134</v>
       </c>
       <c r="L33" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M33" t="s">
         <v>124</v>
@@ -4154,7 +4154,7 @@
         <v>124</v>
       </c>
       <c r="W33" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="X33" t="s">
         <v>124</v>
@@ -4169,7 +4169,7 @@
         <v>124</v>
       </c>
       <c r="AB33" t="n">
-        <v>0.009361505</v>
+        <v>0.0110654</v>
       </c>
       <c r="AC33" t="s">
         <v>217</v>
@@ -4216,7 +4216,7 @@
         <v>134</v>
       </c>
       <c r="L34" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M34" t="s">
         <v>124</v>
@@ -4249,7 +4249,7 @@
         <v>124</v>
       </c>
       <c r="W34" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X34" t="s">
         <v>124</v>
@@ -4264,7 +4264,7 @@
         <v>124</v>
       </c>
       <c r="AB34" t="n">
-        <v>0.011288919</v>
+        <v>0.009810562</v>
       </c>
       <c r="AC34" t="s">
         <v>217</v>
@@ -4311,7 +4311,7 @@
         <v>134</v>
       </c>
       <c r="L35" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M35" t="s">
         <v>124</v>
@@ -4344,7 +4344,7 @@
         <v>124</v>
       </c>
       <c r="W35" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="X35" t="s">
         <v>124</v>
@@ -4359,7 +4359,7 @@
         <v>124</v>
       </c>
       <c r="AB35" t="n">
-        <v>0.009401165</v>
+        <v>0.011313336</v>
       </c>
       <c r="AC35" t="s">
         <v>217</v>
@@ -4406,7 +4406,7 @@
         <v>134</v>
       </c>
       <c r="L36" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M36" t="s">
         <v>124</v>
@@ -4439,7 +4439,7 @@
         <v>124</v>
       </c>
       <c r="W36" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X36" t="s">
         <v>124</v>
@@ -4454,7 +4454,7 @@
         <v>124</v>
       </c>
       <c r="AB36" t="n">
-        <v>0.01111347</v>
+        <v>0.068002978</v>
       </c>
       <c r="AC36" t="s">
         <v>217</v>
@@ -4501,7 +4501,7 @@
         <v>134</v>
       </c>
       <c r="L37" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M37" t="s">
         <v>124</v>
@@ -4534,7 +4534,7 @@
         <v>124</v>
       </c>
       <c r="W37" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="X37" t="s">
         <v>124</v>
@@ -4549,7 +4549,7 @@
         <v>124</v>
       </c>
       <c r="AB37" t="n">
-        <v>0.009485241</v>
+        <v>0.0786813</v>
       </c>
       <c r="AC37" t="s">
         <v>217</v>
@@ -4596,7 +4596,7 @@
         <v>134</v>
       </c>
       <c r="L38" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M38" t="s">
         <v>124</v>
@@ -4629,7 +4629,7 @@
         <v>124</v>
       </c>
       <c r="W38" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X38" t="s">
         <v>124</v>
@@ -4644,7 +4644,7 @@
         <v>124</v>
       </c>
       <c r="AB38" t="n">
-        <v>0.0786813</v>
+        <v>0.009485241</v>
       </c>
       <c r="AC38" t="s">
         <v>217</v>
@@ -4691,7 +4691,7 @@
         <v>134</v>
       </c>
       <c r="L39" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M39" t="s">
         <v>124</v>
@@ -4724,7 +4724,7 @@
         <v>124</v>
       </c>
       <c r="W39" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="X39" t="s">
         <v>124</v>
@@ -4739,7 +4739,7 @@
         <v>124</v>
       </c>
       <c r="AB39" t="n">
-        <v>0.068002978</v>
+        <v>0.01111347</v>
       </c>
       <c r="AC39" t="s">
         <v>217</v>
@@ -4786,7 +4786,7 @@
         <v>134</v>
       </c>
       <c r="L40" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M40" t="s">
         <v>124</v>
@@ -4819,7 +4819,7 @@
         <v>124</v>
       </c>
       <c r="W40" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X40" t="s">
         <v>124</v>
@@ -4834,7 +4834,7 @@
         <v>124</v>
       </c>
       <c r="AB40" t="n">
-        <v>0.011313336</v>
+        <v>0.009401165</v>
       </c>
       <c r="AC40" t="s">
         <v>217</v>
@@ -4881,7 +4881,7 @@
         <v>134</v>
       </c>
       <c r="L41" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M41" t="s">
         <v>124</v>
@@ -4914,7 +4914,7 @@
         <v>124</v>
       </c>
       <c r="W41" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="X41" t="s">
         <v>124</v>
@@ -4929,7 +4929,7 @@
         <v>124</v>
       </c>
       <c r="AB41" t="n">
-        <v>0.009810562</v>
+        <v>0.011288919</v>
       </c>
       <c r="AC41" t="s">
         <v>217</v>
@@ -4976,7 +4976,7 @@
         <v>134</v>
       </c>
       <c r="L42" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M42" t="s">
         <v>124</v>
@@ -5009,7 +5009,7 @@
         <v>124</v>
       </c>
       <c r="W42" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="X42" t="s">
         <v>124</v>
@@ -5024,7 +5024,7 @@
         <v>124</v>
       </c>
       <c r="AB42" t="n">
-        <v>0.0110654</v>
+        <v>0.009361505</v>
       </c>
       <c r="AC42" t="s">
         <v>217</v>
@@ -5104,7 +5104,7 @@
         <v>124</v>
       </c>
       <c r="W43" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="X43" t="s">
         <v>124</v>
@@ -5119,7 +5119,7 @@
         <v>124</v>
       </c>
       <c r="AB43" t="n">
-        <v>0.010758853</v>
+        <v>0.011095322</v>
       </c>
       <c r="AC43" t="s">
         <v>217</v>
@@ -5166,7 +5166,7 @@
         <v>134</v>
       </c>
       <c r="L44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M44" t="s">
         <v>124</v>
@@ -5199,7 +5199,7 @@
         <v>124</v>
       </c>
       <c r="W44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="X44" t="s">
         <v>124</v>
@@ -5214,7 +5214,7 @@
         <v>124</v>
       </c>
       <c r="AB44" t="n">
-        <v>0.062337475</v>
+        <v>0.009416124</v>
       </c>
       <c r="AC44" t="s">
         <v>217</v>
@@ -5294,7 +5294,7 @@
         <v>124</v>
       </c>
       <c r="W45" t="s">
-        <v>174</v>
+        <v>158</v>
       </c>
       <c r="X45" t="s">
         <v>124</v>
@@ -5309,7 +5309,7 @@
         <v>124</v>
       </c>
       <c r="AB45" t="n">
-        <v>0.060152037</v>
+        <v>0.004239412</v>
       </c>
       <c r="AC45" t="s">
         <v>217</v>
@@ -5356,7 +5356,7 @@
         <v>134</v>
       </c>
       <c r="L46" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M46" t="s">
         <v>124</v>
@@ -5389,7 +5389,7 @@
         <v>124</v>
       </c>
       <c r="W46" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="X46" t="s">
         <v>124</v>
@@ -5404,7 +5404,7 @@
         <v>124</v>
       </c>
       <c r="AB46" t="n">
-        <v>0.017650786</v>
+        <v>0.014288217</v>
       </c>
       <c r="AC46" t="s">
         <v>217</v>
@@ -5451,7 +5451,7 @@
         <v>134</v>
       </c>
       <c r="L47" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M47" t="s">
         <v>124</v>
@@ -5484,7 +5484,7 @@
         <v>124</v>
       </c>
       <c r="W47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="X47" t="s">
         <v>124</v>
@@ -5499,7 +5499,7 @@
         <v>124</v>
       </c>
       <c r="AB47" t="n">
-        <v>0.015234293</v>
+        <v>0.015222432</v>
       </c>
       <c r="AC47" t="s">
         <v>217</v>
@@ -5546,7 +5546,7 @@
         <v>134</v>
       </c>
       <c r="L48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M48" t="s">
         <v>124</v>
@@ -5579,7 +5579,7 @@
         <v>124</v>
       </c>
       <c r="W48" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="X48" t="s">
         <v>124</v>
@@ -5594,7 +5594,7 @@
         <v>124</v>
       </c>
       <c r="AB48" t="n">
-        <v>0.017745472</v>
+        <v>0.014039795</v>
       </c>
       <c r="AC48" t="s">
         <v>217</v>
@@ -5689,7 +5689,7 @@
         <v>124</v>
       </c>
       <c r="AB49" t="n">
-        <v>0.015358091</v>
+        <v>0.031932413</v>
       </c>
       <c r="AC49" t="s">
         <v>217</v>
@@ -5769,7 +5769,7 @@
         <v>124</v>
       </c>
       <c r="W50" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="X50" t="s">
         <v>124</v>
@@ -5784,7 +5784,7 @@
         <v>124</v>
       </c>
       <c r="AB50" t="n">
-        <v>0.018102119</v>
+        <v>0.024544266</v>
       </c>
       <c r="AC50" t="s">
         <v>217</v>
@@ -5879,7 +5879,7 @@
         <v>124</v>
       </c>
       <c r="AB51" t="n">
-        <v>0.015385153</v>
+        <v>0.005459863</v>
       </c>
       <c r="AC51" t="s">
         <v>217</v>
@@ -5959,7 +5959,7 @@
         <v>124</v>
       </c>
       <c r="W52" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="X52" t="s">
         <v>124</v>
@@ -5974,7 +5974,7 @@
         <v>124</v>
       </c>
       <c r="AB52" t="n">
-        <v>0.017715821</v>
+        <v>0.004400825</v>
       </c>
       <c r="AC52" t="s">
         <v>217</v>
@@ -6069,7 +6069,7 @@
         <v>124</v>
       </c>
       <c r="AB53" t="n">
-        <v>0.015273349</v>
+        <v>0.005624833</v>
       </c>
       <c r="AC53" t="s">
         <v>217</v>
@@ -6149,7 +6149,7 @@
         <v>124</v>
       </c>
       <c r="W54" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="X54" t="s">
         <v>124</v>
@@ -6164,7 +6164,7 @@
         <v>124</v>
       </c>
       <c r="AB54" t="n">
-        <v>0.114579297</v>
+        <v>0.004944183</v>
       </c>
       <c r="AC54" t="s">
         <v>217</v>
@@ -6259,7 +6259,7 @@
         <v>124</v>
       </c>
       <c r="AB55" t="n">
-        <v>0.100334681</v>
+        <v>0.005789925</v>
       </c>
       <c r="AC55" t="s">
         <v>217</v>
@@ -6339,7 +6339,7 @@
         <v>124</v>
       </c>
       <c r="W56" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="X56" t="s">
         <v>124</v>
@@ -6354,7 +6354,7 @@
         <v>124</v>
       </c>
       <c r="AB56" t="n">
-        <v>0.015472817</v>
+        <v>0.005426907</v>
       </c>
       <c r="AC56" t="s">
         <v>217</v>
@@ -6401,7 +6401,7 @@
         <v>134</v>
       </c>
       <c r="L57" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M57" t="s">
         <v>124</v>
@@ -6434,7 +6434,7 @@
         <v>124</v>
       </c>
       <c r="W57" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X57" t="s">
         <v>124</v>
@@ -6449,7 +6449,7 @@
         <v>124</v>
       </c>
       <c r="AB57" t="n">
-        <v>0.012185883</v>
+        <v>0.045655947</v>
       </c>
       <c r="AC57" t="s">
         <v>217</v>
@@ -6496,7 +6496,7 @@
         <v>134</v>
       </c>
       <c r="L58" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M58" t="s">
         <v>124</v>
@@ -6529,7 +6529,7 @@
         <v>124</v>
       </c>
       <c r="W58" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="X58" t="s">
         <v>124</v>
@@ -6544,7 +6544,7 @@
         <v>124</v>
       </c>
       <c r="AB58" t="n">
-        <v>0.01462736</v>
+        <v>0.042025038</v>
       </c>
       <c r="AC58" t="s">
         <v>217</v>
@@ -6591,7 +6591,7 @@
         <v>134</v>
       </c>
       <c r="L59" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M59" t="s">
         <v>124</v>
@@ -6624,7 +6624,7 @@
         <v>124</v>
       </c>
       <c r="W59" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X59" t="s">
         <v>124</v>
@@ -6639,7 +6639,7 @@
         <v>124</v>
       </c>
       <c r="AB59" t="n">
-        <v>0.00117488</v>
+        <v>0.006878595</v>
       </c>
       <c r="AC59" t="s">
         <v>217</v>
@@ -6686,7 +6686,7 @@
         <v>134</v>
       </c>
       <c r="L60" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M60" t="s">
         <v>124</v>
@@ -6719,7 +6719,7 @@
         <v>124</v>
       </c>
       <c r="W60" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="X60" t="s">
         <v>124</v>
@@ -6734,7 +6734,7 @@
         <v>124</v>
       </c>
       <c r="AB60" t="n">
-        <v>0.001588894</v>
+        <v>0.006495451</v>
       </c>
       <c r="AC60" t="s">
         <v>217</v>
@@ -6781,7 +6781,7 @@
         <v>134</v>
       </c>
       <c r="L61" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M61" t="s">
         <v>124</v>
@@ -6814,7 +6814,7 @@
         <v>124</v>
       </c>
       <c r="W61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X61" t="s">
         <v>124</v>
@@ -6829,7 +6829,7 @@
         <v>124</v>
       </c>
       <c r="AB61" t="n">
-        <v>0.000989828</v>
+        <v>0.006971473</v>
       </c>
       <c r="AC61" t="s">
         <v>217</v>
@@ -6876,7 +6876,7 @@
         <v>134</v>
       </c>
       <c r="L62" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M62" t="s">
         <v>124</v>
@@ -6909,7 +6909,7 @@
         <v>124</v>
       </c>
       <c r="W62" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="X62" t="s">
         <v>124</v>
@@ -6924,7 +6924,7 @@
         <v>124</v>
       </c>
       <c r="AB62" t="n">
-        <v>0.001467165</v>
+        <v>0.006923147</v>
       </c>
       <c r="AC62" t="s">
         <v>217</v>
@@ -6971,7 +6971,7 @@
         <v>134</v>
       </c>
       <c r="L63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M63" t="s">
         <v>124</v>
@@ -7004,7 +7004,7 @@
         <v>124</v>
       </c>
       <c r="W63" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X63" t="s">
         <v>124</v>
@@ -7019,7 +7019,7 @@
         <v>124</v>
       </c>
       <c r="AB63" t="n">
-        <v>0.000781829</v>
+        <v>0.032248067</v>
       </c>
       <c r="AC63" t="s">
         <v>217</v>
@@ -7066,7 +7066,7 @@
         <v>134</v>
       </c>
       <c r="L64" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M64" t="s">
         <v>124</v>
@@ -7099,7 +7099,7 @@
         <v>124</v>
       </c>
       <c r="W64" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="X64" t="s">
         <v>124</v>
@@ -7114,7 +7114,7 @@
         <v>124</v>
       </c>
       <c r="AB64" t="n">
-        <v>0.001480606</v>
+        <v>0.025999723</v>
       </c>
       <c r="AC64" t="s">
         <v>217</v>
@@ -7161,7 +7161,7 @@
         <v>134</v>
       </c>
       <c r="L65" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M65" t="s">
         <v>124</v>
@@ -7194,7 +7194,7 @@
         <v>124</v>
       </c>
       <c r="W65" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X65" t="s">
         <v>124</v>
@@ -7209,7 +7209,7 @@
         <v>124</v>
       </c>
       <c r="AB65" t="n">
-        <v>0.005686357</v>
+        <v>0.00559294</v>
       </c>
       <c r="AC65" t="s">
         <v>217</v>
@@ -7256,7 +7256,7 @@
         <v>134</v>
       </c>
       <c r="L66" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M66" t="s">
         <v>124</v>
@@ -7289,7 +7289,7 @@
         <v>124</v>
       </c>
       <c r="W66" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="X66" t="s">
         <v>124</v>
@@ -7304,7 +7304,7 @@
         <v>124</v>
       </c>
       <c r="AB66" t="n">
-        <v>0.009812113</v>
+        <v>0.005558036</v>
       </c>
       <c r="AC66" t="s">
         <v>217</v>
@@ -7351,7 +7351,7 @@
         <v>134</v>
       </c>
       <c r="L67" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M67" t="s">
         <v>124</v>
@@ -7384,7 +7384,7 @@
         <v>124</v>
       </c>
       <c r="W67" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X67" t="s">
         <v>124</v>
@@ -7399,7 +7399,7 @@
         <v>124</v>
       </c>
       <c r="AB67" t="n">
-        <v>0.021674355</v>
+        <v>0.005548685</v>
       </c>
       <c r="AC67" t="s">
         <v>217</v>
@@ -7446,7 +7446,7 @@
         <v>134</v>
       </c>
       <c r="L68" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M68" t="s">
         <v>124</v>
@@ -7479,7 +7479,7 @@
         <v>124</v>
       </c>
       <c r="W68" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="X68" t="s">
         <v>124</v>
@@ -7494,7 +7494,7 @@
         <v>124</v>
       </c>
       <c r="AB68" t="n">
-        <v>0.022727369</v>
+        <v>0.005703369</v>
       </c>
       <c r="AC68" t="s">
         <v>217</v>
@@ -7541,7 +7541,7 @@
         <v>134</v>
       </c>
       <c r="L69" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M69" t="s">
         <v>124</v>
@@ -7574,7 +7574,7 @@
         <v>124</v>
       </c>
       <c r="W69" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="X69" t="s">
         <v>124</v>
@@ -7589,7 +7589,7 @@
         <v>124</v>
       </c>
       <c r="AB69" t="n">
-        <v>0.006514123</v>
+        <v>0.005512073</v>
       </c>
       <c r="AC69" t="s">
         <v>217</v>
@@ -7669,7 +7669,7 @@
         <v>124</v>
       </c>
       <c r="W70" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="X70" t="s">
         <v>124</v>
@@ -7684,7 +7684,7 @@
         <v>124</v>
       </c>
       <c r="AB70" t="n">
-        <v>0.024250153</v>
+        <v>0.006213158</v>
       </c>
       <c r="AC70" t="s">
         <v>217</v>
@@ -7764,7 +7764,7 @@
         <v>124</v>
       </c>
       <c r="W71" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="X71" t="s">
         <v>124</v>
@@ -7779,7 +7779,7 @@
         <v>124</v>
       </c>
       <c r="AB71" t="n">
-        <v>0.023058507</v>
+        <v>0.043013646</v>
       </c>
       <c r="AC71" t="s">
         <v>217</v>
@@ -7859,7 +7859,7 @@
         <v>124</v>
       </c>
       <c r="W72" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="X72" t="s">
         <v>124</v>
@@ -7874,7 +7874,7 @@
         <v>124</v>
       </c>
       <c r="AB72" t="n">
-        <v>0.007498418</v>
+        <v>0.049322095</v>
       </c>
       <c r="AC72" t="s">
         <v>217</v>
@@ -7954,7 +7954,7 @@
         <v>124</v>
       </c>
       <c r="W73" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="X73" t="s">
         <v>124</v>
@@ -7969,7 +7969,7 @@
         <v>124</v>
       </c>
       <c r="AB73" t="n">
-        <v>0.006690431</v>
+        <v>0.006954877</v>
       </c>
       <c r="AC73" t="s">
         <v>217</v>
@@ -8049,7 +8049,7 @@
         <v>124</v>
       </c>
       <c r="W74" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="X74" t="s">
         <v>124</v>
@@ -8064,7 +8064,7 @@
         <v>124</v>
       </c>
       <c r="AB74" t="n">
-        <v>0.007857064</v>
+        <v>0.007374454</v>
       </c>
       <c r="AC74" t="s">
         <v>217</v>
@@ -8144,7 +8144,7 @@
         <v>124</v>
       </c>
       <c r="W75" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="X75" t="s">
         <v>124</v>
@@ -8159,7 +8159,7 @@
         <v>124</v>
       </c>
       <c r="AB75" t="n">
-        <v>0.007080464</v>
+        <v>0.007274797</v>
       </c>
       <c r="AC75" t="s">
         <v>217</v>
@@ -8239,7 +8239,7 @@
         <v>124</v>
       </c>
       <c r="W76" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="X76" t="s">
         <v>124</v>
@@ -8334,7 +8334,7 @@
         <v>124</v>
       </c>
       <c r="W77" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="X77" t="s">
         <v>124</v>
@@ -8349,7 +8349,7 @@
         <v>124</v>
       </c>
       <c r="AB77" t="n">
-        <v>0.007274797</v>
+        <v>0.007080464</v>
       </c>
       <c r="AC77" t="s">
         <v>217</v>
@@ -8429,7 +8429,7 @@
         <v>124</v>
       </c>
       <c r="W78" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="X78" t="s">
         <v>124</v>
@@ -8444,7 +8444,7 @@
         <v>124</v>
       </c>
       <c r="AB78" t="n">
-        <v>0.007374454</v>
+        <v>0.007857064</v>
       </c>
       <c r="AC78" t="s">
         <v>217</v>
@@ -8524,7 +8524,7 @@
         <v>124</v>
       </c>
       <c r="W79" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="X79" t="s">
         <v>124</v>
@@ -8539,7 +8539,7 @@
         <v>124</v>
       </c>
       <c r="AB79" t="n">
-        <v>0.006954877</v>
+        <v>0.006690431</v>
       </c>
       <c r="AC79" t="s">
         <v>217</v>
@@ -8619,7 +8619,7 @@
         <v>124</v>
       </c>
       <c r="W80" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="X80" t="s">
         <v>124</v>
@@ -8634,7 +8634,7 @@
         <v>124</v>
       </c>
       <c r="AB80" t="n">
-        <v>0.049322095</v>
+        <v>0.007498418</v>
       </c>
       <c r="AC80" t="s">
         <v>217</v>
@@ -8714,7 +8714,7 @@
         <v>124</v>
       </c>
       <c r="W81" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="X81" t="s">
         <v>124</v>
@@ -8729,7 +8729,7 @@
         <v>124</v>
       </c>
       <c r="AB81" t="n">
-        <v>0.043013646</v>
+        <v>0.023058507</v>
       </c>
       <c r="AC81" t="s">
         <v>217</v>
@@ -8809,7 +8809,7 @@
         <v>124</v>
       </c>
       <c r="W82" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
       <c r="X82" t="s">
         <v>124</v>
@@ -8824,7 +8824,7 @@
         <v>124</v>
       </c>
       <c r="AB82" t="n">
-        <v>0.006213158</v>
+        <v>0.024250153</v>
       </c>
       <c r="AC82" t="s">
         <v>217</v>
@@ -8904,7 +8904,7 @@
         <v>124</v>
       </c>
       <c r="W83" t="s">
-        <v>194</v>
+        <v>152</v>
       </c>
       <c r="X83" t="s">
         <v>124</v>
@@ -8919,7 +8919,7 @@
         <v>124</v>
       </c>
       <c r="AB83" t="n">
-        <v>0.005558036</v>
+        <v>0.006514123</v>
       </c>
       <c r="AC83" t="s">
         <v>217</v>
@@ -8999,7 +8999,7 @@
         <v>124</v>
       </c>
       <c r="W84" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="X84" t="s">
         <v>124</v>
@@ -9014,7 +9014,7 @@
         <v>124</v>
       </c>
       <c r="AB84" t="n">
-        <v>0.00559294</v>
+        <v>0.022727369</v>
       </c>
       <c r="AC84" t="s">
         <v>217</v>
@@ -9094,7 +9094,7 @@
         <v>124</v>
       </c>
       <c r="W85" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="X85" t="s">
         <v>124</v>
@@ -9109,7 +9109,7 @@
         <v>124</v>
       </c>
       <c r="AB85" t="n">
-        <v>0.025999723</v>
+        <v>0.021674355</v>
       </c>
       <c r="AC85" t="s">
         <v>217</v>
@@ -9189,7 +9189,7 @@
         <v>124</v>
       </c>
       <c r="W86" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="X86" t="s">
         <v>124</v>
@@ -9204,7 +9204,7 @@
         <v>124</v>
       </c>
       <c r="AB86" t="n">
-        <v>0.032248067</v>
+        <v>0.009812113</v>
       </c>
       <c r="AC86" t="s">
         <v>217</v>
@@ -9284,7 +9284,7 @@
         <v>124</v>
       </c>
       <c r="W87" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="X87" t="s">
         <v>124</v>
@@ -9299,7 +9299,7 @@
         <v>124</v>
       </c>
       <c r="AB87" t="n">
-        <v>0.007518359</v>
+        <v>0.005686357</v>
       </c>
       <c r="AC87" t="s">
         <v>217</v>
@@ -9379,7 +9379,7 @@
         <v>124</v>
       </c>
       <c r="W88" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="X88" t="s">
         <v>124</v>
@@ -9394,7 +9394,7 @@
         <v>124</v>
       </c>
       <c r="AB88" t="n">
-        <v>0.008188906</v>
+        <v>0.001480606</v>
       </c>
       <c r="AC88" t="s">
         <v>217</v>
@@ -9474,7 +9474,7 @@
         <v>124</v>
       </c>
       <c r="W89" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="X89" t="s">
         <v>124</v>
@@ -9489,7 +9489,7 @@
         <v>124</v>
       </c>
       <c r="AB89" t="n">
-        <v>0.002350475</v>
+        <v>0.000781829</v>
       </c>
       <c r="AC89" t="s">
         <v>217</v>
@@ -9569,7 +9569,7 @@
         <v>124</v>
       </c>
       <c r="W90" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="X90" t="s">
         <v>124</v>
@@ -9584,7 +9584,7 @@
         <v>124</v>
       </c>
       <c r="AB90" t="n">
-        <v>0.002326722</v>
+        <v>0.001467165</v>
       </c>
       <c r="AC90" t="s">
         <v>217</v>
@@ -9664,7 +9664,7 @@
         <v>124</v>
       </c>
       <c r="W91" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="X91" t="s">
         <v>124</v>
@@ -9679,7 +9679,7 @@
         <v>124</v>
       </c>
       <c r="AB91" t="n">
-        <v>0.002537856</v>
+        <v>0.000989828</v>
       </c>
       <c r="AC91" t="s">
         <v>217</v>
@@ -9759,7 +9759,7 @@
         <v>124</v>
       </c>
       <c r="W92" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="X92" t="s">
         <v>124</v>
@@ -9774,7 +9774,7 @@
         <v>124</v>
       </c>
       <c r="AB92" t="n">
-        <v>0.002438007</v>
+        <v>0.001588894</v>
       </c>
       <c r="AC92" t="s">
         <v>217</v>
@@ -9854,7 +9854,7 @@
         <v>124</v>
       </c>
       <c r="W93" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="X93" t="s">
         <v>124</v>
@@ -9869,7 +9869,7 @@
         <v>124</v>
       </c>
       <c r="AB93" t="n">
-        <v>0.002380284</v>
+        <v>0.00117488</v>
       </c>
       <c r="AC93" t="s">
         <v>217</v>
@@ -9949,7 +9949,7 @@
         <v>124</v>
       </c>
       <c r="W94" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="X94" t="s">
         <v>124</v>
@@ -9964,7 +9964,7 @@
         <v>124</v>
       </c>
       <c r="AB94" t="n">
-        <v>0.002498876</v>
+        <v>0.01462736</v>
       </c>
       <c r="AC94" t="s">
         <v>217</v>
@@ -10044,7 +10044,7 @@
         <v>124</v>
       </c>
       <c r="W95" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="X95" t="s">
         <v>124</v>
@@ -10059,7 +10059,7 @@
         <v>124</v>
       </c>
       <c r="AB95" t="n">
-        <v>0.001969919</v>
+        <v>0.012185883</v>
       </c>
       <c r="AC95" t="s">
         <v>217</v>
@@ -10106,7 +10106,7 @@
         <v>134</v>
       </c>
       <c r="L96" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M96" t="s">
         <v>124</v>
@@ -10139,7 +10139,7 @@
         <v>124</v>
       </c>
       <c r="W96" t="s">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="X96" t="s">
         <v>124</v>
@@ -10154,7 +10154,7 @@
         <v>124</v>
       </c>
       <c r="AB96" t="n">
-        <v>0.002444422</v>
+        <v>0.015472817</v>
       </c>
       <c r="AC96" t="s">
         <v>217</v>
@@ -10234,7 +10234,7 @@
         <v>124</v>
       </c>
       <c r="W97" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="X97" t="s">
         <v>124</v>
@@ -10249,7 +10249,7 @@
         <v>124</v>
       </c>
       <c r="AB97" t="n">
-        <v>0.006423248</v>
+        <v>0.100334681</v>
       </c>
       <c r="AC97" t="s">
         <v>217</v>
@@ -10329,7 +10329,7 @@
         <v>124</v>
       </c>
       <c r="W98" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="X98" t="s">
         <v>124</v>
@@ -10344,7 +10344,7 @@
         <v>124</v>
       </c>
       <c r="AB98" t="n">
-        <v>0.006931423</v>
+        <v>0.114579297</v>
       </c>
       <c r="AC98" t="s">
         <v>217</v>
@@ -10424,7 +10424,7 @@
         <v>124</v>
       </c>
       <c r="W99" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="X99" t="s">
         <v>124</v>
@@ -10439,7 +10439,7 @@
         <v>124</v>
       </c>
       <c r="AB99" t="n">
-        <v>0.006738811</v>
+        <v>0.015273349</v>
       </c>
       <c r="AC99" t="s">
         <v>217</v>
@@ -10486,7 +10486,7 @@
         <v>134</v>
       </c>
       <c r="L100" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M100" t="s">
         <v>124</v>
@@ -10519,7 +10519,7 @@
         <v>124</v>
       </c>
       <c r="W100" t="s">
-        <v>159</v>
+        <v>200</v>
       </c>
       <c r="X100" t="s">
         <v>124</v>
@@ -10534,7 +10534,7 @@
         <v>124</v>
       </c>
       <c r="AB100" t="n">
-        <v>0.031932413</v>
+        <v>0.017715821</v>
       </c>
       <c r="AC100" t="s">
         <v>217</v>
@@ -10614,7 +10614,7 @@
         <v>124</v>
       </c>
       <c r="W101" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="X101" t="s">
         <v>124</v>
@@ -10629,7 +10629,7 @@
         <v>124</v>
       </c>
       <c r="AB101" t="n">
-        <v>0.014039795</v>
+        <v>0.015385153</v>
       </c>
       <c r="AC101" t="s">
         <v>217</v>
@@ -10709,7 +10709,7 @@
         <v>124</v>
       </c>
       <c r="W102" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="X102" t="s">
         <v>124</v>
@@ -10724,7 +10724,7 @@
         <v>124</v>
       </c>
       <c r="AB102" t="n">
-        <v>0.015222432</v>
+        <v>0.018102119</v>
       </c>
       <c r="AC102" t="s">
         <v>217</v>
@@ -10819,7 +10819,7 @@
         <v>124</v>
       </c>
       <c r="AB103" t="n">
-        <v>0.014288217</v>
+        <v>0.015358091</v>
       </c>
       <c r="AC103" t="s">
         <v>217</v>
@@ -10899,7 +10899,7 @@
         <v>124</v>
       </c>
       <c r="W104" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="X104" t="s">
         <v>124</v>
@@ -10914,7 +10914,7 @@
         <v>124</v>
       </c>
       <c r="AB104" t="n">
-        <v>0.01394809</v>
+        <v>0.017745472</v>
       </c>
       <c r="AC104" t="s">
         <v>217</v>
@@ -11009,7 +11009,7 @@
         <v>124</v>
       </c>
       <c r="AB105" t="n">
-        <v>0.014058032</v>
+        <v>0.015234293</v>
       </c>
       <c r="AC105" t="s">
         <v>217</v>
@@ -11089,7 +11089,7 @@
         <v>124</v>
       </c>
       <c r="W106" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="X106" t="s">
         <v>124</v>
@@ -11104,7 +11104,7 @@
         <v>124</v>
       </c>
       <c r="AB106" t="n">
-        <v>0.065697347</v>
+        <v>0.017650786</v>
       </c>
       <c r="AC106" t="s">
         <v>217</v>
@@ -11199,7 +11199,7 @@
         <v>124</v>
       </c>
       <c r="AB107" t="n">
-        <v>0.080785628</v>
+        <v>0.060152037</v>
       </c>
       <c r="AC107" t="s">
         <v>217</v>
@@ -11279,7 +11279,7 @@
         <v>124</v>
       </c>
       <c r="W108" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="X108" t="s">
         <v>124</v>
@@ -11294,7 +11294,7 @@
         <v>124</v>
       </c>
       <c r="AB108" t="n">
-        <v>0.013371994</v>
+        <v>0.062337475</v>
       </c>
       <c r="AC108" t="s">
         <v>217</v>
@@ -11341,7 +11341,7 @@
         <v>134</v>
       </c>
       <c r="L109" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M109" t="s">
         <v>124</v>
@@ -11374,7 +11374,7 @@
         <v>124</v>
       </c>
       <c r="W109" t="s">
-        <v>205</v>
+        <v>173</v>
       </c>
       <c r="X109" t="s">
         <v>124</v>
@@ -11389,7 +11389,7 @@
         <v>124</v>
       </c>
       <c r="AB109" t="n">
-        <v>0.016337457</v>
+        <v>0.010758853</v>
       </c>
       <c r="AC109" t="s">
         <v>217</v>
@@ -11436,7 +11436,7 @@
         <v>134</v>
       </c>
       <c r="L110" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M110" t="s">
         <v>124</v>
@@ -11469,7 +11469,7 @@
         <v>124</v>
       </c>
       <c r="W110" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X110" t="s">
         <v>124</v>
@@ -11484,7 +11484,7 @@
         <v>124</v>
       </c>
       <c r="AB110" t="n">
-        <v>0.004342057</v>
+        <v>0.036646967</v>
       </c>
       <c r="AC110" t="s">
         <v>217</v>
@@ -11531,7 +11531,7 @@
         <v>134</v>
       </c>
       <c r="L111" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M111" t="s">
         <v>124</v>
@@ -11564,7 +11564,7 @@
         <v>124</v>
       </c>
       <c r="W111" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="X111" t="s">
         <v>124</v>
@@ -11579,7 +11579,7 @@
         <v>124</v>
       </c>
       <c r="AB111" t="n">
-        <v>0.004127151</v>
+        <v>0.037675262</v>
       </c>
       <c r="AC111" t="s">
         <v>217</v>
@@ -11626,7 +11626,7 @@
         <v>134</v>
       </c>
       <c r="L112" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M112" t="s">
         <v>124</v>
@@ -11659,7 +11659,7 @@
         <v>124</v>
       </c>
       <c r="W112" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X112" t="s">
         <v>124</v>
@@ -11674,7 +11674,7 @@
         <v>124</v>
       </c>
       <c r="AB112" t="n">
-        <v>0.004582276</v>
+        <v>0.02187069</v>
       </c>
       <c r="AC112" t="s">
         <v>217</v>
@@ -11721,7 +11721,7 @@
         <v>134</v>
       </c>
       <c r="L113" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M113" t="s">
         <v>124</v>
@@ -11754,7 +11754,7 @@
         <v>124</v>
       </c>
       <c r="W113" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="X113" t="s">
         <v>124</v>
@@ -11769,7 +11769,7 @@
         <v>124</v>
       </c>
       <c r="AB113" t="n">
-        <v>0.00416601</v>
+        <v>0.015902671</v>
       </c>
       <c r="AC113" t="s">
         <v>217</v>
@@ -11816,7 +11816,7 @@
         <v>134</v>
       </c>
       <c r="L114" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M114" t="s">
         <v>124</v>
@@ -11849,7 +11849,7 @@
         <v>124</v>
       </c>
       <c r="W114" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X114" t="s">
         <v>124</v>
@@ -11864,7 +11864,7 @@
         <v>124</v>
       </c>
       <c r="AB114" t="n">
-        <v>0.004690154</v>
+        <v>0.003792878</v>
       </c>
       <c r="AC114" t="s">
         <v>217</v>
@@ -11911,7 +11911,7 @@
         <v>134</v>
       </c>
       <c r="L115" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M115" t="s">
         <v>124</v>
@@ -11944,7 +11944,7 @@
         <v>124</v>
       </c>
       <c r="W115" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="X115" t="s">
         <v>124</v>
@@ -11959,7 +11959,7 @@
         <v>124</v>
       </c>
       <c r="AB115" t="n">
-        <v>0.004193503</v>
+        <v>0.002924553</v>
       </c>
       <c r="AC115" t="s">
         <v>217</v>
@@ -12006,7 +12006,7 @@
         <v>134</v>
       </c>
       <c r="L116" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M116" t="s">
         <v>124</v>
@@ -12039,7 +12039,7 @@
         <v>124</v>
       </c>
       <c r="W116" t="s">
-        <v>166</v>
+        <v>208</v>
       </c>
       <c r="X116" t="s">
         <v>124</v>
@@ -12054,7 +12054,7 @@
         <v>124</v>
       </c>
       <c r="AB116" t="n">
-        <v>0.004516368</v>
+        <v>0.003855268</v>
       </c>
       <c r="AC116" t="s">
         <v>217</v>
@@ -12101,7 +12101,7 @@
         <v>134</v>
       </c>
       <c r="L117" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M117" t="s">
         <v>124</v>
@@ -12134,7 +12134,7 @@
         <v>124</v>
       </c>
       <c r="W117" t="s">
-        <v>173</v>
+        <v>208</v>
       </c>
       <c r="X117" t="s">
         <v>124</v>
@@ -12149,7 +12149,7 @@
         <v>124</v>
       </c>
       <c r="AB117" t="n">
-        <v>0.009772012</v>
+        <v>0.003281807</v>
       </c>
       <c r="AC117" t="s">
         <v>217</v>
@@ -12196,7 +12196,7 @@
         <v>134</v>
       </c>
       <c r="L118" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M118" t="s">
         <v>124</v>
@@ -12244,7 +12244,7 @@
         <v>124</v>
       </c>
       <c r="AB118" t="n">
-        <v>0.010118339</v>
+        <v>0.00392837</v>
       </c>
       <c r="AC118" t="s">
         <v>217</v>
@@ -12291,7 +12291,7 @@
         <v>134</v>
       </c>
       <c r="L119" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M119" t="s">
         <v>124</v>
@@ -12339,7 +12339,7 @@
         <v>124</v>
       </c>
       <c r="AB119" t="n">
-        <v>0.009470893</v>
+        <v>0.003610349</v>
       </c>
       <c r="AC119" t="s">
         <v>217</v>
@@ -12386,7 +12386,7 @@
         <v>134</v>
       </c>
       <c r="L120" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M120" t="s">
         <v>124</v>
@@ -12434,7 +12434,7 @@
         <v>124</v>
       </c>
       <c r="AB120" t="n">
-        <v>0.045285979</v>
+        <v>0.029224619</v>
       </c>
       <c r="AC120" t="s">
         <v>217</v>
@@ -12481,7 +12481,7 @@
         <v>134</v>
       </c>
       <c r="L121" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M121" t="s">
         <v>124</v>
@@ -12529,7 +12529,7 @@
         <v>124</v>
       </c>
       <c r="AB121" t="n">
-        <v>0.053937877</v>
+        <v>0.030742214</v>
       </c>
       <c r="AC121" t="s">
         <v>217</v>
